--- a/data/trans_dic/P57_AF_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P57_AF_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo afectivo bajo (Duke)</t>
+          <t>Población con apoyo afectivo bajo (Duke) (tasa de respuesta: 99,39%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>46,07; 55,2</t>
+          <t>46,68; 55,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>50,48; 60,45</t>
+          <t>50,77; 60,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64,72; 73,79</t>
+          <t>64,87; 74,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27,95; 43,92</t>
+          <t>28,12; 44,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>50,83; 60,15</t>
+          <t>51,17; 60,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,19; 61,98</t>
+          <t>52,18; 61,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,48; 73,12</t>
+          <t>63,77; 72,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>35,19; 50,45</t>
+          <t>36,3; 50,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>49,9; 56,27</t>
+          <t>50,25; 56,16</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52,76; 59,59</t>
+          <t>52,79; 59,62</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65,68; 72,33</t>
+          <t>65,66; 72,4</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>34,05; 44,87</t>
+          <t>33,53; 45,45</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>55,01; 62,34</t>
+          <t>54,67; 62,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>53,59; 61,7</t>
+          <t>53,77; 61,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>71,57; 78,82</t>
+          <t>71,66; 78,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46,21; 59,6</t>
+          <t>46,92; 59,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>53,03; 60,97</t>
+          <t>53,29; 61,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>61,78; 69,3</t>
+          <t>61,66; 69,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>69,42; 77,12</t>
+          <t>70,07; 77,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>24,73; 49,56</t>
+          <t>25,32; 48,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>55,35; 60,47</t>
+          <t>55,3; 60,67</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58,35; 63,88</t>
+          <t>58,68; 64,19</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>71,78; 76,94</t>
+          <t>71,79; 76,85</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>33,81; 51,89</t>
+          <t>35,3; 51,91</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>56,9; 64,15</t>
+          <t>56,9; 64,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>61,52; 68,98</t>
+          <t>61,51; 69,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>69,52; 76,55</t>
+          <t>69,74; 76,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>51,56; 60,82</t>
+          <t>51,74; 60,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>55,38; 63,04</t>
+          <t>55,6; 63,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>61,75; 69,09</t>
+          <t>61,23; 69,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>69,1; 76,05</t>
+          <t>68,91; 75,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>50,96; 58,27</t>
+          <t>50,82; 58,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>57,59; 63,14</t>
+          <t>57,41; 62,79</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>62,75; 67,9</t>
+          <t>62,51; 67,92</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>70,58; 75,45</t>
+          <t>70,57; 75,46</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>52,69; 58,31</t>
+          <t>52,71; 58,21</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>57,67; 66,58</t>
+          <t>57,78; 66,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>59,49; 67,47</t>
+          <t>59,49; 67,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>72,3; 79,34</t>
+          <t>72,57; 79,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,62; 57,72</t>
+          <t>19,07; 57,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>56,81; 65,3</t>
+          <t>57,35; 65,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,72; 76,19</t>
+          <t>68,77; 76,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,54; 80,46</t>
+          <t>73,8; 80,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>46,63; 59,78</t>
+          <t>46,45; 59,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>58,83; 65,13</t>
+          <t>58,8; 64,92</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65,16; 70,74</t>
+          <t>65,08; 70,73</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74,42; 79,26</t>
+          <t>74,09; 78,82</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>27,85; 57,23</t>
+          <t>29,83; 57,43</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>59,17; 68,66</t>
+          <t>59,43; 69,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>53,82; 63,9</t>
+          <t>54,12; 64,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69,01; 77,44</t>
+          <t>68,88; 77,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57,52; 65,29</t>
+          <t>57,13; 65,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>61,8; 70,93</t>
+          <t>61,64; 70,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,14; 73,02</t>
+          <t>64,12; 73,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>74,3; 81,83</t>
+          <t>74,12; 82,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>60,34; 66,39</t>
+          <t>60,7; 66,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>62,04; 68,63</t>
+          <t>61,5; 68,9</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>60,89; 67,49</t>
+          <t>60,6; 67,33</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72,81; 78,49</t>
+          <t>72,77; 78,59</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>59,91; 64,99</t>
+          <t>59,95; 64,99</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>62,25; 72,99</t>
+          <t>62,06; 72,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>61,68; 72,21</t>
+          <t>61,28; 72,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>66,45; 76,49</t>
+          <t>66,58; 76,42</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>57,68; 66,29</t>
+          <t>58,05; 66,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>59,69; 69,23</t>
+          <t>59,32; 69,42</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>65,24; 74,99</t>
+          <t>65,01; 75,06</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>75,92; 84,62</t>
+          <t>76,26; 84,06</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>59,87; 89,86</t>
+          <t>59,35; 89,73</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>62,15; 69,74</t>
+          <t>62,15; 69,05</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>64,77; 72,34</t>
+          <t>64,91; 72,26</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>72,79; 79,09</t>
+          <t>73,07; 79,68</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>60,43; 83,71</t>
+          <t>60,87; 83,25</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>65,72; 77,57</t>
+          <t>66,07; 78,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>64,25; 76,7</t>
+          <t>64,87; 77,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>73,21; 82,38</t>
+          <t>73,02; 82,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>62,85; 71,33</t>
+          <t>62,56; 71,8</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>64,13; 75,06</t>
+          <t>64,0; 74,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,52; 72,93</t>
+          <t>63,03; 72,93</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,2; 87,73</t>
+          <t>79,43; 87,85</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>67,25; 73,23</t>
+          <t>67,26; 73,35</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>66,71; 74,86</t>
+          <t>66,56; 75,07</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>65,22; 72,64</t>
+          <t>64,43; 72,57</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>78,19; 84,5</t>
+          <t>77,98; 84,43</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>66,14; 71,9</t>
+          <t>66,2; 71,63</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>59,15; 62,57</t>
+          <t>59,03; 62,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>60,1; 63,56</t>
+          <t>60,17; 63,6</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>72,31; 75,45</t>
+          <t>72,4; 75,46</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39,25; 56,51</t>
+          <t>40,43; 56,59</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>59,51; 62,8</t>
+          <t>59,65; 62,91</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>65,2; 68,51</t>
+          <t>65,13; 68,46</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>74,56; 77,49</t>
+          <t>74,67; 77,5</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>54,62; 65,2</t>
+          <t>54,5; 65,87</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>59,81; 62,09</t>
+          <t>59,72; 62,11</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>63,27; 65,54</t>
+          <t>63,26; 65,65</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>74,01; 76,13</t>
+          <t>73,99; 76,09</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>49,44; 58,84</t>
+          <t>49,44; 59,25</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo afectivo bajo (Duke)</t>
+          <t>Población con apoyo afectivo bajo (Duke) (tasa de respuesta: 99,39%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>227214; 272259</t>
+          <t>230241; 272973</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>227746; 272723</t>
+          <t>229058; 273821</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>271482; 309510</t>
+          <t>272094; 312374</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>111328; 174956</t>
+          <t>112021; 177846</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>237603; 281201</t>
+          <t>239224; 282418</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>224016; 266048</t>
+          <t>223984; 263236</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>251231; 289386</t>
+          <t>252371; 288286</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>110221; 158012</t>
+          <t>113699; 159037</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>479439; 540600</t>
+          <t>482807; 539497</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>464476; 524604</t>
+          <t>464798; 524912</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>535398; 589658</t>
+          <t>535256; 590188</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>242289; 319296</t>
+          <t>238602; 323383</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>404615; 458476</t>
+          <t>402070; 456843</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>366024; 421413</t>
+          <t>367281; 420426</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>420181; 462753</t>
+          <t>420691; 460924</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>195111; 251633</t>
+          <t>198116; 250898</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>331161; 380750</t>
+          <t>332790; 382613</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>375707; 421406</t>
+          <t>374978; 422544</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>388866; 431990</t>
+          <t>392510; 431851</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>126203; 252965</t>
+          <t>129234; 249224</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>752762; 822340</t>
+          <t>752094; 825152</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>753336; 824828</t>
+          <t>757690; 828778</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>823471; 882673</t>
+          <t>823660; 881670</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>315338; 483953</t>
+          <t>329250; 484159</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>362762; 408993</t>
+          <t>362766; 413024</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>418727; 469526</t>
+          <t>418650; 471389</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>464573; 511563</t>
+          <t>465992; 511650</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>274542; 323889</t>
+          <t>275492; 323617</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>381461; 434189</t>
+          <t>382985; 436772</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>436273; 488157</t>
+          <t>432637; 487499</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>451268; 496671</t>
+          <t>450022; 495751</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>275722; 315311</t>
+          <t>274966; 313939</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>763847; 837432</t>
+          <t>761488; 832793</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>870479; 941884</t>
+          <t>867199; 942163</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>932585; 996907</t>
+          <t>932402; 997037</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>565706; 626055</t>
+          <t>565942; 624922</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>299374; 345629</t>
+          <t>299947; 346834</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>363222; 411968</t>
+          <t>363267; 412740</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>464331; 509493</t>
+          <t>466063; 509102</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>163788; 507649</t>
+          <t>167703; 509005</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>292940; 336708</t>
+          <t>295734; 338915</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>420115; 465760</t>
+          <t>420418; 464889</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>477351; 522237</t>
+          <t>479038; 522146</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>328631; 421339</t>
+          <t>327396; 420064</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>608724; 673976</t>
+          <t>608478; 671743</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>796188; 864352</t>
+          <t>795247; 864317</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>960902; 1023488</t>
+          <t>956676; 1017767</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>441213; 906605</t>
+          <t>472505; 909860</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>228327; 264935</t>
+          <t>229308; 266763</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>230017; 273116</t>
+          <t>231292; 274250</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>326095; 365896</t>
+          <t>325474; 366450</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>320285; 363516</t>
+          <t>318126; 363027</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>249673; 286558</t>
+          <t>248999; 286759</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>285258; 324755</t>
+          <t>285142; 326848</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>366693; 403848</t>
+          <t>365791; 405076</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>325832; 358475</t>
+          <t>327747; 360564</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>489995; 542055</t>
+          <t>485766; 544224</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>531012; 588632</t>
+          <t>528470; 587183</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>703402; 758217</t>
+          <t>702982; 759215</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>657050; 712775</t>
+          <t>657460; 712835</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>181057; 212266</t>
+          <t>180483; 211862</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>188181; 220302</t>
+          <t>186974; 220305</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>221544; 255007</t>
+          <t>221973; 254767</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>211686; 243292</t>
+          <t>213060; 243566</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>204712; 237428</t>
+          <t>203428; 238064</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>227340; 261324</t>
+          <t>226543; 261558</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>286051; 318833</t>
+          <t>287356; 316744</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>362341; 543836</t>
+          <t>359178; 543019</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>393862; 441979</t>
+          <t>393901; 437599</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>423328; 472764</t>
+          <t>424215; 472300</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>516904; 561684</t>
+          <t>518953; 565839</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>587502; 813852</t>
+          <t>591775; 809327</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>137926; 162804</t>
+          <t>138661; 163926</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>159226; 190073</t>
+          <t>160766; 191072</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>187526; 210991</t>
+          <t>187017; 210743</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>174243; 197755</t>
+          <t>173434; 199039</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>214142; 250629</t>
+          <t>213708; 249374</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>239817; 279716</t>
+          <t>241756; 279711</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>314831; 348747</t>
+          <t>315741; 349225</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>279013; 303854</t>
+          <t>279066; 304338</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>362741; 407059</t>
+          <t>361940; 408250</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>411782; 458631</t>
+          <t>406797; 458207</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>511078; 552334</t>
+          <t>509702; 551865</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>457800; 497643</t>
+          <t>458166; 495736</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1935520; 2047449</t>
+          <t>1931499; 2040308</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2047014; 2164819</t>
+          <t>2049151; 2166148</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2443440; 2549433</t>
+          <t>2446255; 2549832</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1347645; 1940319</t>
+          <t>1388323; 1943104</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2009712; 2120774</t>
+          <t>2014386; 2124563</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2303002; 2419673</t>
+          <t>2300373; 2417984</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2628925; 2732085</t>
+          <t>2632941; 2732581</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1982363; 2366368</t>
+          <t>1978061; 2390665</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3977174; 4128712</t>
+          <t>3970701; 4129880</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4389377; 4546755</t>
+          <t>4388709; 4554484</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5110015; 5256477</t>
+          <t>5108940; 5254090</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>3491972; 4156024</t>
+          <t>3491842; 4185170</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P57_AF_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P57_AF_R-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>41,88%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>46,68; 55,34</t>
+          <t>46,69; 55,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>50,77; 60,69</t>
+          <t>50,83; 60,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64,87; 74,47</t>
+          <t>65,34; 74,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28,12; 44,65</t>
+          <t>30,96; 46,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>51,17; 60,41</t>
+          <t>50,92; 60,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,18; 61,32</t>
+          <t>52,08; 61,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,77; 72,84</t>
+          <t>64,78; 73,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>36,3; 50,78</t>
+          <t>38,59; 52,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>50,25; 56,16</t>
+          <t>50,43; 56,54</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52,79; 59,62</t>
+          <t>52,86; 59,69</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65,66; 72,4</t>
+          <t>65,66; 72,13</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>33,53; 45,45</t>
+          <t>36,98; 47,35</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>54,87%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>52,03%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>54,67; 62,11</t>
+          <t>54,93; 62,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>53,77; 61,55</t>
+          <t>53,44; 61,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>71,66; 78,51</t>
+          <t>71,49; 78,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46,92; 59,43</t>
+          <t>49,13; 60,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>53,29; 61,27</t>
+          <t>53,21; 61,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>61,66; 69,49</t>
+          <t>61,64; 69,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70,07; 77,1</t>
+          <t>69,46; 77,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>25,32; 48,83</t>
+          <t>44,57; 54,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>55,3; 60,67</t>
+          <t>55,06; 60,45</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58,68; 64,19</t>
+          <t>58,65; 64,31</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>71,79; 76,85</t>
+          <t>71,81; 76,85</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>35,3; 51,91</t>
+          <t>48,49; 55,9</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>55,73%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>56,74%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>56,9; 64,78</t>
+          <t>56,76; 64,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>61,51; 69,25</t>
+          <t>61,33; 68,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>69,74; 76,57</t>
+          <t>69,73; 76,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>51,74; 60,77</t>
+          <t>53,21; 62,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>55,6; 63,41</t>
+          <t>56,16; 63,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>61,23; 69,0</t>
+          <t>61,49; 69,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>68,91; 75,91</t>
+          <t>68,76; 76,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>50,82; 58,02</t>
+          <t>52,53; 58,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>57,41; 62,79</t>
+          <t>57,25; 62,8</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>62,51; 67,92</t>
+          <t>62,68; 67,83</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>70,57; 75,46</t>
+          <t>70,55; 75,4</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>52,71; 58,21</t>
+          <t>53,92; 59,32</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>57,87%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>57,78; 66,81</t>
+          <t>57,63; 66,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>59,49; 67,6</t>
+          <t>59,26; 67,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>72,57; 79,28</t>
+          <t>72,57; 79,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,07; 57,88</t>
+          <t>53,07; 60,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>57,35; 65,73</t>
+          <t>56,91; 65,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,77; 76,04</t>
+          <t>68,55; 76,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,8; 80,44</t>
+          <t>73,46; 80,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>46,45; 59,6</t>
+          <t>56,28; 61,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>58,8; 64,92</t>
+          <t>58,7; 65,12</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65,08; 70,73</t>
+          <t>65,48; 71,1</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74,09; 78,82</t>
+          <t>74,25; 79,07</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29,83; 57,43</t>
+          <t>55,36; 60,18</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>62,69%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>59,43; 69,13</t>
+          <t>59,22; 68,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>54,12; 64,17</t>
+          <t>54,5; 64,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>68,88; 77,55</t>
+          <t>69,0; 77,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57,13; 65,2</t>
+          <t>58,67; 66,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>61,64; 70,98</t>
+          <t>61,46; 70,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,12; 73,49</t>
+          <t>64,41; 73,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>74,12; 82,08</t>
+          <t>73,92; 81,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>60,7; 66,78</t>
+          <t>59,88; 66,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>61,5; 68,9</t>
+          <t>61,91; 68,52</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>60,6; 67,33</t>
+          <t>60,79; 67,49</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72,77; 78,59</t>
+          <t>72,84; 78,92</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>59,95; 64,99</t>
+          <t>60,3; 65,3</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>61,58%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>62,06; 72,85</t>
+          <t>61,95; 72,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>61,28; 72,21</t>
+          <t>61,27; 72,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>66,58; 76,42</t>
+          <t>66,49; 76,91</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>58,05; 66,36</t>
+          <t>58,08; 66,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>59,32; 69,42</t>
+          <t>59,5; 69,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>65,01; 75,06</t>
+          <t>65,48; 75,25</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>76,26; 84,06</t>
+          <t>75,8; 84,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>59,35; 89,73</t>
+          <t>57,29; 64,12</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>62,15; 69,05</t>
+          <t>61,98; 69,2</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>64,91; 72,26</t>
+          <t>64,77; 72,26</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>73,07; 79,68</t>
+          <t>73,21; 79,49</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>60,87; 83,25</t>
+          <t>58,95; 64,16</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,35%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,17%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>66,07; 78,1</t>
+          <t>65,85; 77,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>64,87; 77,1</t>
+          <t>64,01; 76,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>73,02; 82,28</t>
+          <t>73,12; 82,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>62,56; 71,8</t>
+          <t>62,56; 71,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>64,0; 74,68</t>
+          <t>64,78; 75,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,03; 72,93</t>
+          <t>62,67; 72,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,43; 87,85</t>
+          <t>79,06; 87,98</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>67,26; 73,35</t>
+          <t>67,1; 73,77</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>66,56; 75,07</t>
+          <t>66,63; 74,59</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>64,43; 72,57</t>
+          <t>65,1; 72,71</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>77,98; 84,43</t>
+          <t>78,16; 84,56</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>66,2; 71,63</t>
+          <t>66,49; 71,74</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>57,61%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>59,03; 62,36</t>
+          <t>58,95; 62,32</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>60,17; 63,6</t>
+          <t>60,38; 63,69</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>72,4; 75,46</t>
+          <t>72,36; 75,49</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40,43; 56,59</t>
+          <t>54,97; 58,84</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>59,65; 62,91</t>
+          <t>59,65; 62,89</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>65,13; 68,46</t>
+          <t>65,15; 68,44</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>74,67; 77,5</t>
+          <t>74,53; 77,51</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>54,5; 65,87</t>
+          <t>56,62; 59,7</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>59,72; 62,11</t>
+          <t>59,76; 62,22</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>63,26; 65,65</t>
+          <t>63,18; 65,65</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>73,99; 76,09</t>
+          <t>74,07; 76,07</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>49,44; 59,25</t>
+          <t>56,41; 58,84</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>142713</t>
+          <t>155363</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>135451</t>
+          <t>166502</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>278164</t>
+          <t>321865</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>230241; 272973</t>
+          <t>230286; 273628</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>229058; 273821</t>
+          <t>229305; 272883</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>272094; 312374</t>
+          <t>274062; 312077</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>112021; 177846</t>
+          <t>125685; 187776</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>239224; 282418</t>
+          <t>238057; 280564</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>223984; 263236</t>
+          <t>223543; 264479</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>252371; 288286</t>
+          <t>256367; 288997</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>113699; 159037</t>
+          <t>139907; 190659</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>482807; 539497</t>
+          <t>484460; 543208</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>464798; 524912</t>
+          <t>465338; 525524</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>535256; 590188</t>
+          <t>535252; 587988</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>238602; 323383</t>
+          <t>284159; 363845</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>225736</t>
+          <t>260916</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>209296</t>
+          <t>246219</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>435031</t>
+          <t>507136</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>402070; 456843</t>
+          <t>403975; 458579</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>367281; 420426</t>
+          <t>365007; 418668</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>420691; 460924</t>
+          <t>419721; 461662</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>198116; 250898</t>
+          <t>233627; 290063</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>332790; 382613</t>
+          <t>332326; 381674</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>374978; 422544</t>
+          <t>374829; 423679</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>392510; 431851</t>
+          <t>389102; 431312</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>129234; 249224</t>
+          <t>222443; 271677</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>752094; 825152</t>
+          <t>748829; 822110</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>757690; 828778</t>
+          <t>757283; 830383</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>823660; 881670</t>
+          <t>823880; 881636</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>329250; 484159</t>
+          <t>472572; 544835</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>299598</t>
+          <t>354899</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>295351</t>
+          <t>345932</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>594949</t>
+          <t>700831</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>362766; 413024</t>
+          <t>361909; 413087</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>418650; 471389</t>
+          <t>417454; 469165</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>465992; 511650</t>
+          <t>465959; 512423</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>275492; 323617</t>
+          <t>326870; 381044</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>382985; 436772</t>
+          <t>386781; 438157</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>432637; 487499</t>
+          <t>434439; 489082</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>450022; 495751</t>
+          <t>449035; 497108</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>274966; 313939</t>
+          <t>326107; 366105</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>761488; 832793</t>
+          <t>759334; 832937</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>867199; 942163</t>
+          <t>869451; 940877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>932402; 997037</t>
+          <t>932127; 996341</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>565942; 624922</t>
+          <t>665938; 732607</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>357146</t>
+          <t>392540</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>393249</t>
+          <t>429232</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>750395</t>
+          <t>821773</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>299947; 346834</t>
+          <t>299193; 346550</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>363267; 412740</t>
+          <t>361856; 412042</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>466063; 509102</t>
+          <t>466021; 512276</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>167703; 509005</t>
+          <t>367379; 421078</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>295734; 338915</t>
+          <t>293477; 340199</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>420418; 464889</t>
+          <t>419103; 464724</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>479038; 522146</t>
+          <t>476806; 520444</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>327396; 420064</t>
+          <t>409600; 450857</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>608478; 671743</t>
+          <t>607405; 673818</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>795247; 864317</t>
+          <t>800087; 868752</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>956676; 1017767</t>
+          <t>958787; 1020951</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>472505; 909860</t>
+          <t>786192; 854569</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>342500</t>
+          <t>375846</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>342915</t>
+          <t>379377</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>685415</t>
+          <t>755224</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>229308; 266763</t>
+          <t>228494; 265417</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>231292; 274250</t>
+          <t>232928; 274139</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>325474; 366450</t>
+          <t>326058; 366785</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>318126; 363027</t>
+          <t>354958; 402905</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>248999; 286759</t>
+          <t>248301; 285882</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>285142; 326848</t>
+          <t>286455; 326559</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>365791; 405076</t>
+          <t>364806; 404318</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>327747; 360564</t>
+          <t>359056; 396086</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>485766; 544224</t>
+          <t>488967; 541167</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>528470; 587183</t>
+          <t>530191; 588633</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>702982; 759215</t>
+          <t>703630; 762405</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>657460; 712835</t>
+          <t>726417; 786650</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>227592</t>
+          <t>252378</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>448114</t>
+          <t>266024</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>675706</t>
+          <t>518402</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>180483; 211862</t>
+          <t>180172; 210951</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>186974; 220305</t>
+          <t>186926; 220133</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>221973; 254767</t>
+          <t>221679; 256412</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>213060; 243566</t>
+          <t>235799; 268710</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>203428; 238064</t>
+          <t>204035; 238463</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>226543; 261558</t>
+          <t>228168; 262220</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>287356; 316744</t>
+          <t>285590; 318523</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>359178; 543019</t>
+          <t>249671; 279433</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>393901; 437599</t>
+          <t>392784; 438571</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>424215; 472300</t>
+          <t>423303; 472296</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>518953; 565839</t>
+          <t>519917; 564545</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>591775; 809327</t>
+          <t>496263; 540109</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>186492</t>
+          <t>205092</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>292414</t>
+          <t>318874</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>478906</t>
+          <t>523967</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>138661; 163926</t>
+          <t>138208; 163552</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>160766; 191072</t>
+          <t>158629; 189567</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>187017; 210743</t>
+          <t>187291; 212015</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>173434; 199039</t>
+          <t>190499; 218043</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>213708; 249374</t>
+          <t>216301; 251648</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>241756; 279711</t>
+          <t>240363; 276505</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>315741; 349225</t>
+          <t>314267; 349729</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>279066; 304338</t>
+          <t>303977; 334186</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>361940; 408250</t>
+          <t>362326; 405602</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>406797; 458207</t>
+          <t>410999; 459089</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>509702; 551865</t>
+          <t>510889; 552711</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>458166; 495736</t>
+          <t>503653; 543481</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1781775</t>
+          <t>1997035</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2116789</t>
+          <t>2152162</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>3898565</t>
+          <t>4149198</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1931499; 2040308</t>
+          <t>1929022; 2039205</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2049151; 2166148</t>
+          <t>2056241; 2169055</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2446255; 2549832</t>
+          <t>2444893; 2550717</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1388323; 1943104</t>
+          <t>1925935; 2061694</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2014386; 2124563</t>
+          <t>2014582; 2123827</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2300373; 2417984</t>
+          <t>2301178; 2417346</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2632941; 2732581</t>
+          <t>2627909; 2732923</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1978061; 2390665</t>
+          <t>2093941; 2208051</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3970701; 4129880</t>
+          <t>3973465; 4136987</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4388709; 4554484</t>
+          <t>4383012; 4554313</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5108940; 5254090</t>
+          <t>5114418; 5252865</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>3491842; 4185170</t>
+          <t>4062573; 4237959</t>
         </is>
       </c>
     </row>
